--- a/pensum/ok04/OK04_Regnskapsanalyse_Oppgaver_v6.xlsx
+++ b/pensum/ok04/OK04_Regnskapsanalyse_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="147">
   <si>
     <t xml:space="preserve">Regnskapsanalyse: oppgaver til kapittel 4</t>
   </si>
@@ -65,10 +65,19 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Driften er bedre enn totalkapitalrentabiliteten viser</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Nordlys: 47,9 % til eierne. Hva er det som løfter?</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapitalrentabiliteten regnes etter skatt</t>
   </si>
   <si>
     <t xml:space="preserve">Situasjonen</t>
@@ -166,7 +175,16 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingenting: overskuddet står på bankkontoen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Nordlys: tåler bedriften 600 000 kr i utbytte?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overskuddet er et resultat, ikke en beholdning: pengene står mest i kundefordringer og varelager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overskuddet er feil regnet, fordi skatten ikke er trukket fra</t>
   </si>
   <si>
     <t xml:space="preserve">Det er januar 2027, og årsregnskapet for 2026 er klart med et årsresultat på 910 650 kr. Tom Berg vil ta ut 600 000 kr i utbytte: «Pengene finnes, vi hadde jo overskudd.» Utbyttet skal betales fra bankkontoen. Kari Nordlund vil vite hva det gjør med betalingsevnen og soliditeten før hun svarer, for banken skal fornye kassekreditten i mars.</t>
@@ -236,7 +254,13 @@
     <t xml:space="preserve">g) Hva svarer Kari? To setninger: hva utbyttet gjør med betalingsevnen og soliditeten, og hva hun foreslår i stedet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bedrer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Fjell Elektro etter første år: det banken leser før den sier ja til bilen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Svekker</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS i Oslo har drevet i ett år. Eieren vil kjøpe en tredje servicebil for 400 000 kr på nytt banklån, og banken ber om årsregnskapet først. Du er den som skal legge fram tallene: lønnsomhet, likviditet og soliditet, og si hva som er sterkt og hva som er svakt. Sammenlikn med bransjen: elektrobedriftene i NHO Elektros lønnsomhetsrapport 2025 hadde totalkapitalrentabilitet 14,6 %, driftsresultat 7,5 % av omsetningen, likviditetsgrad 1 på 190 %, likviditetsgrad 2 på 160 % og egenkapitalandel 36,4 %.</t>
@@ -641,7 +665,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -664,6 +688,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1114,7 +1142,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G40"/>
+  <dimension ref="B1:Z40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1122,343 +1150,355 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>23</v>
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="n">
         <v>22400000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="n">
         <v>1344000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="n">
         <v>232500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="n">
         <v>1167500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="n">
         <v>910650</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>9400000</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>10182650</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>1982000</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>2892650</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="B19" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>7418000</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <v>7290000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="B21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="B22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-((9400000+10182650)/2))&lt;=1,"Riktig.",IF(ABS(C24-(10182650))&lt;=1,"Du har brukt bare tallet 31. desember. Kapitalen har arbeidet hele året: ta (1. januar + 31. desember) / 2.",IF(ABS(C24-(9400000+10182650))&lt;=1,"Du har lagt sammen de to tallene, men ikke delt på to.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(ABS(C25-(ROUND(1344000/22400000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C25-(ROUND(910650/22400000*100,1)))&lt;=0.06,"Du har brukt årsresultatet. Driftsmarginen bruker driftsresultatet, før renter og skatt.",IF(ABS(C25-(ROUND(1167500/22400000*100,1)))&lt;=0.06,"Du har brukt resultat før skatt. Driftsmarginen bruker driftsresultatet, før rentene.",IF(ABS(C25-(ROUND(1344000/22400000,1)))&lt;=0.06,"Du har glemt å gange med 100. Svar i prosent: 6,0.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(ABS(C26-(ROUND((1167500+232500)/((9400000+10182650)/2)*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C26-(ROUND(1167500/((9400000+10182650)/2)*100,1)))&lt;=0.06,"Du har glemt å legge rentekostnadene tilbake i telleren. Rentene er bankens del av det kapitalen tjener.",IF(ABS(C26-(ROUND((1167500+232500)/10182650*100,1)))&lt;=0.06,"Du har delt på totalkapitalen 31. desember alene. Bruk gjennomsnittet fra a.",IF(ABS(C26-(ROUND(910650/((9400000+10182650)/2)*100,1)))&lt;=0.06,"Du har brukt årsresultatet etter skatt. Boka regner før skatt, og legger rentene til.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(ROUND(232500/((7418000+7290000)/2)*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C27-(ROUND(232500/2800000*100,1)))&lt;=0.06,"Du har delt på banklånet alene. Gjeldsrenta i boka regnes av all gjeld, også den rentefrie (grossisten, staten, feriepengene).",IF(ABS(C27-(7.5))&lt;=0.06,"7,5 % er bankens rente på lånet. Gjennomsnittlig gjeldsrente er rentekostnadene delt på all gjeld i snitt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="16" t="str">
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND(1167500/((1982000+2892650)/2)*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C28-(ROUND(910650/((1982000+2892650)/2)*100,1)))&lt;=0.06,"Du har brukt årsresultatet. Boka regner egenkapitalrentabiliteten av resultat før skatt.",IF(ABS(C28-(ROUND(1167500/2892650*100,1)))&lt;=0.06,"Du har delt på egenkapitalen 31. desember alene. Bruk gjennomsnittet av 1. januar og 31. desember.",IF(ABS(C28-(ROUND((1167500+232500)/((1982000+2892650)/2)*100,1)))&lt;=0.06,"Du har lagt rentene til. Rentene er bankens, ikke eiernes; her er telleren resultat før skatt uten rentene.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital","Riktig. Kapitalen tjener 14,3 %, gjelden koster 3,2 % i snitt. Differansen går til eierne, og den deles på en egenkapital som bare er 28,4 % av totalkapitalen. Det er gjelden som løfter, ikke driften. Begge tallene regnes før skatt.","Ikke riktig. Kapitalen tjener 14,3 %, gjelden koster 3,2 % i snitt. Differansen går til eierne, og den deles på en egenkapital som bare er 28,4 % av totalkapitalen. Det er gjelden som løfter, ikke driften. Begge tallene regnes før skatt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="B32" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="20" t="str">
+      <c r="B36" s="21" t="str">
         <f aca="false">IF(LEN(B33)&lt;40,"",IF(AND(ISNUMBER(SEARCH("dårlig",B33)),ISNUMBER(SEARCH("egenkapital",B33))),"Bra: du har med både at gjelden tar fra egenkapitalen i et dårlig år, og at banken ser på egenkapitalen før den låner ut mer.",IF(OR(ISNUMBER(SEARCH("dårlig",B33)),ISNUMBER(SEARCH("egenkapital",B33))),"Du er på sporet. Si også hva som skjer i et dårlig år, når kapitalen tjener mindre enn renta koster, og hva banken ser på.","Tips: gjelden virker begge veier. I et dårlig år er rentene de samme, og tapet tas av en egenkapital på bare 28,4 %. Nye lån koster bankens 7,5 %, ikke snittet på 3,2 %, og banken ser egenkapitalandelen falle til 23,7 %.")))</f>
         <v/>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="18"/>
+      <c r="B37" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="22" t="str">
+      <c r="B38" s="23" t="str">
         <f aca="false">IF(C37="JA","Hint: a: (9 400 000 + 10 182 650) / 2 = 9 791 325. b: 1 344 000 × 100 / 22 400 000 = 6,0. c: (1 167 500 + 232 500) × 100 / 9 791 325 = 14,3. d: gjennomsnittlig gjeld (7 418 000 + 7 290 000) / 2 = 7 354 000; 232 500 × 100 / 7 354 000 = 3,2. e: gjennomsnittlig egenkapital (1 982 000 + 2 892 650) / 2 = 2 437 325; 1 167 500 × 100 / 2 437 325 = 47,9.","")</f>
         <v/>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1528,7 +1568,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Driften er bedre enn totalkapitalrentabiliteten viser,Gjelden koster mindre enn kapitalen tjener,og gevinsten deles på en liten egenkapital,Egenkapitalrentabiliteten regnes etter skatt"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
@@ -1551,7 +1591,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G41"/>
+  <dimension ref="B1:Z41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1559,334 +1599,346 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>50</v>
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>3600000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>1400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>4200000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>982650</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>6582650</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>10182650</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>2892650</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="B19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>2800000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="B20" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>4490000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="B22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="B23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(ABS(C25-(ROUND(6582650/4490000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C25-(ROUND(6582650/7290000*100,1)))&lt;=0.06,"Du har delt på all gjeld. Likviditetsgraden bruker bare den kortsiktige gjelden, det som forfaller i år.",IF(ABS(C25-(ROUND((6582650-1400000)/4490000*100,1)))&lt;=0.06,"Du har trukket fra varelageret. Det er likviditetsgrad 2. Grad 1 bruker alle omløpsmidlene.",IF(ABS(C25-(ROUND(10182650/4490000*100,1)))&lt;=0.06,"Du har brukt sum eiendeler. Anleggsmidlene er ikke med: bilene kan ikke betale lønn på fredag.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(ABS(C26-(ROUND((6582650-1400000)/4490000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C26-(ROUND(6582650/4490000*100,1)))&lt;=0.06,"Det er likviditetsgrad 1. I grad 2 trekker du varelageret fra omløpsmidlene.",IF(ABS(C26-(ROUND((6582650-4200000)/4490000*100,1)))&lt;=0.06,"Du har trukket fra kundefordringene. Det er varelageret som holdes utenfor i grad 2, fordi det er det minst likvide.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(ROUND((6582650-600000)/4490000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C27-(ROUND(6582650/4490000*100,1)))&lt;=0.06,"Du har ikke trukket utbyttet fra bankinnskuddet. Omløpsmidlene blir 600 000 mindre.",IF(ABS(C27-(ROUND(6582650/(4490000+600000)*100,1)))&lt;=0.06,"Du har lagt utbyttet til den kortsiktige gjelden. Når det er betalt ut fra banken, er det borte fra omløpsmidlene og fra egenkapitalen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND((6582650-600000-1400000)/4490000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C28-(ROUND((6582650-1400000)/4490000*100,1)))&lt;=0.06,"Du har ikke trukket utbyttet fra. Bankinnskuddet er 600 000 mindre.",IF(ABS(C28-(ROUND((6582650-600000)/4490000*100,1)))&lt;=0.06,"Det er likviditetsgrad 1 etter utbyttet. Trekk også fra varelageret.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(ABS(C29-(ROUND((2892650-600000)/(10182650-600000)*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C29-(ROUND((2892650-600000)/10182650*100,1)))&lt;=0.06,"Du har trukket utbyttet fra egenkapitalen, men ikke fra totalkapitalen. Pengene gikk ut av banken, så sum eiendeler er også 600 000 mindre.",IF(ABS(C29-(ROUND(2892650/10182650*100,1)))&lt;=0.06,"Det er egenkapitalandelen i dag, før utbyttet. Trekk 600 000 fra både egenkapital og totalkapital.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Overskuddet er et resultat, ikke en beholdning: pengene står mest i kundefordringer og varelager","Riktig. Årsresultatet sier at bedriften har tjent penger, ikke hvor pengene er. Av omløpsmidlene på 6 582 650 står 4 200 000 hos kundene og 1 400 000 på lageret. På konto står 982 650. Skatten er allerede trukket fra i årsresultatet.","Ikke riktig. Årsresultatet sier at bedriften har tjent penger, ikke hvor pengene er. Av omløpsmidlene på 6 582 650 står 4 200 000 hos kundene og 1 400 000 på lageret. På konto står 982 650. Skatten er allerede trukket fra i årsresultatet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="B33" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="20" t="str">
+      <c r="B37" s="21" t="str">
         <f aca="false">IF(LEN(B34)&lt;40,"",IF(AND(ISNUMBER(SEARCH("likviditet",B34)),ISNUMBER(SEARCH("egenkapital",B34))),"Bra: du har med både likviditeten og egenkapitalen. Sjekk at du også har et forslag: et mindre utbytte, eller la overskuddet stå til kundene har betalt.",IF(OR(ISNUMBER(SEARCH("likviditet",B34)),ISNUMBER(SEARCH("egenkapital",B34))),"Du har med det ene. Si både hva som skjer med likviditetsgraden (102,1 % i grad 2) og med egenkapitalandelen (23,9 %), og hva Kari foreslår i stedet.","Tips: likviditetsgrad 2 faller til 102,1 %, så vidt over normtallet, og bankinnskuddet blir 382 650, mindre enn én månedslønn. Egenkapitalandelen faller fra 28,4 % til 23,9 %. Kari kan foreslå å la overskuddet stå (boka 4.2.4.1), eller et mindre utbytte når kundene har betalt.")))</f>
         <v/>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="18"/>
+      <c r="B38" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="22" t="str">
+      <c r="B39" s="23" t="str">
         <f aca="false">IF(C38="JA","Hint: a: 6 582 650 × 100 / 4 490 000 = 146,6. b: (6 582 650 − 1 400 000) × 100 / 4 490 000 = 115,4. c: (6 582 650 − 600 000) × 100 / 4 490 000 = 133,2. d: (5 982 650 − 1 400 000) × 100 / 4 490 000 = 102,1. e: (2 892 650 − 600 000) × 100 / (10 182 650 − 600 000) = 23,9.","")</f>
         <v/>
       </c>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
+      <c r="B41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1956,7 +2008,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Ingenting: overskuddet står på bankkontoen,Overskuddet er et resultat,ikke en beholdning: pengene står mest i kundefordringer og varelager,Overskuddet er feil regnet,fordi skatten ikke er trukket fra"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C38" type="list">
@@ -1979,7 +2031,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G50"/>
+  <dimension ref="B1:Z50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1987,451 +2039,492 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>50</v>
+      <c r="B11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="n">
         <v>4795000</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="n">
         <v>144240</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="n">
         <v>37500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="n">
         <v>106740</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>240000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="12" t="n">
+      <c r="B17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>800000</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>1143257</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>800000</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>1383257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="B19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>300000</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <v>383257</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="B20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>500000</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>400000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="B21" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <v>600000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="B22" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="13" t="n">
         <v>500000</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="13" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="B24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(ROUND(144240/4795000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C27-(ROUND(106740/4795000*100,1)))&lt;=0.06,"Du har brukt resultat før skatt. Driftsmarginen bruker driftsresultatet, før rentene.",IF(ABS(C27-(ROUND(144240/4795000,1)))&lt;=0.06,"Du har glemt å gange med 100.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND((106740+37500)/((800000+1383257)/2)*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C28-(ROUND((106740+37500)/1383257*100,1)))&lt;=0.06,"Du har delt på totalkapitalen 31. desember alene. Bruk gjennomsnittet: (800 000 + 1 383 257) / 2.",IF(ABS(C28-(ROUND(106740/((800000+1383257)/2)*100,1)))&lt;=0.06,"Du har glemt å legge rentekostnadene tilbake i telleren.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(ABS(C29-(ROUND(1143257/600000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C29-(ROUND(1143257/1000000*100,1)))&lt;=0.06,"Du har delt på all gjeld. Bruk bare den kortsiktige gjelden, 600 000.",IF(ABS(C29-(ROUND(563257/600000*100,1)))&lt;=0.06,"Du har brukt bare bankinnskuddet. Omløpsmidlene er varelager, kundefordringer og bank til sammen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Skriv svaret i den gule cellen.",IF(ABS(C30-(ROUND((1143257-80000)/600000*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C30-(ROUND(1143257/600000*100,1)))&lt;=0.06,"Det er likviditetsgrad 1. Trekk varelageret 80 000 fra omløpsmidlene.",IF(ABS(C30-(ROUND((1143257-500000)/600000*100,1)))&lt;=0.06,"Du har trukket fra kundefordringene. Det er varelageret som holdes utenfor.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="16" t="str">
+      <c r="B31" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="17" t="str">
         <f aca="false">IF(C31="","Skriv svaret i den gule cellen.",IF(ABS(C31-(ROUND(383257/1383257*100,1)))&lt;=0.06,"Riktig.",IF(ABS(C31-(ROUND(383257/1000000*100,1)))&lt;=0.06,"Du har delt på gjelden. Egenkapitalandelen deles på totalkapitalen, 1 383 257.",IF(ABS(C31-(ROUND(300000/1383257*100,1)))&lt;=0.06,"Du har brukt bare aksjekapitalen. Egenkapitalen er aksjekapital pluss opptjent egenkapital: 383 257.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" s="16" t="str">
+      <c r="B32" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="17" t="str">
         <f aca="false">IF(C32="","Skriv svaret i den gule cellen.",IF(ABS(C32-(ROUND(1000000/383257,2)))&lt;=0.006,"Riktig.",IF(ABS(C32-(ROUND(383257/1000000,2)))&lt;=0.006,"Du har snudd brøken. Gjeldsgrad er sum gjeld delt på egenkapital.",IF(ABS(C32-(ROUND(400000/383257,2)))&lt;=0.006,"Du har brukt bare banklånet. All gjeld teller: 400 000 + 600 000 = 1 000 000.",IF(ABS(C32-(ROUND(1000000/1383257,2)))&lt;=0.006,"Du har delt på totalkapitalen. Det er gjeldsandelen, ikke gjeldsgraden. Del på egenkapitalen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="B34" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="G35" s="16" t="str">
+      <c r="B35" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="G35" s="17" t="str">
         <f aca="false">IF(C35="","Velg i nedtrekksmenyen.",IF(C35="Bedrer","Riktig. Egenkapitalen øker med 83 257 uten at gjelden øker. Bokas første tiltak (4.2.4.1).","Ikke riktig. Egenkapitalen øker med 83 257 uten at gjelden øker. Bokas første tiltak (4.2.4.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="G36" s="16" t="str">
+      <c r="B36" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="G36" s="17" t="str">
         <f aca="false">IF(C36="","Velg i nedtrekksmenyen.",IF(C36="Bedrer","Riktig. Ny egenkapital fra eieren (4.2.4.1).","Ikke riktig. Ny egenkapital fra eieren (4.2.4.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="G37" s="16" t="str">
+      <c r="B37" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="G37" s="17" t="str">
         <f aca="false">IF(C37="","Velg i nedtrekksmenyen.",IF(C37="Svekker","Riktig. Gjelden og totalkapitalen øker, egenkapitalen står stille. Andelen faller.","Ikke riktig. Gjelden og totalkapitalen øker, egenkapitalen står stille. Andelen faller."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="G38" s="16" t="str">
+      <c r="B38" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="G38" s="17" t="str">
         <f aca="false">IF(C38="","Velg i nedtrekksmenyen.",IF(C38="Bedrer","Riktig. Totalkapitalen blir 100 000 mindre, egenkapitalen er den samme. 383 257 / 1 283 257 = 29,9 %.","Ikke riktig. Totalkapitalen blir 100 000 mindre, egenkapitalen er den samme. 383 257 / 1 283 257 = 29,9 %."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="G39" s="16" t="str">
+      <c r="B39" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="G39" s="17" t="str">
         <f aca="false">IF(C39="","Velg i nedtrekksmenyen.",IF(C39="Svekker","Riktig. Egenkapitalen faller, og totalkapitalen faller like mye. 303 257 / 1 303 257 = 23,3 %.","Ikke riktig. Egenkapitalen faller, og totalkapitalen faller like mye. 303 257 / 1 303 257 = 23,3 %."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="G40" s="16" t="str">
+      <c r="B40" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="G40" s="17" t="str">
         <f aca="false">IF(C40="","Velg i nedtrekksmenyen.",IF(C40="Svekker","Riktig. Totalkapitalen øker med 400 000, egenkapitalen står stille: 383 257 / 1 783 257 = 21,5 %. Bilen er nyttig, men lånet senker andelen uansett.","Ikke riktig. Totalkapitalen øker med 400 000, egenkapitalen står stille: 383 257 / 1 783 257 = 21,5 %. Bilen er nyttig, men lånet senker andelen uansett."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="B42" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="20" t="str">
+      <c r="B46" s="21" t="str">
         <f aca="false">IF(LEN(B43)&lt;40,"",IF(AND(ISNUMBER(SEARCH("lønnsom",B43)),ISNUMBER(SEARCH("egenkapital",B43))),"Bra: du vurderer både lønnsomheten og egenkapitalen. Sjekk at du også sier at likviditeten er god (190,5 %), og at bilen på lån trekker egenkapitalandelen ned til 21,5 %.",IF(OR(ISNUMBER(SEARCH("lønnsom",B43)),ISNUMBER(SEARCH("egenkapital",B43))),"Du har med det ene. Banken ser på alle tre: lønnsomhet (driftsmargin 3,0 %, totalkapitalrentabilitet 13,2 %), likviditet (190,5 % og 177,2 %) og soliditet (27,7 %, gjeldsgrad 2,61).","Tips: kapitalen tjener 13,2 %, godt over bankens 7,5 %, men driftsmarginen på 3,0 % er tynn: tre kroner igjen av hver hundrelapp. Likviditeten er god, 190,5 % og 177,2 %. Egenkapitalandelen 27,7 % er under bransjens 36,4 %, og bilen på lån gir 21,5 %. Banken vil trolig si ja, men be om at overskuddet blir stående.")))</f>
         <v/>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" s="18"/>
+      <c r="B47" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="19"/>
     </row>
     <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="22" t="str">
+      <c r="B48" s="23" t="str">
         <f aca="false">IF(C47="JA","Hint: a: 144 240 × 100 / 4 795 000 = 3,0. b: (106 740 + 37 500) × 100 / 1 091 628,5 = 13,2. c: 1 143 257 × 100 / 600 000 = 190,5. d: (1 143 257 − 80 000) × 100 / 600 000 = 177,2. e: 383 257 × 100 / 1 383 257 = 27,7. f: 1 000 000 / 383 257 = 2,61.","")</f>
         <v/>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
+      <c r="B50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2550,27 +2643,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Bedrer,Svekker"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Bedrer,Svekker"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Bedrer,Svekker"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C38" type="list">
-      <formula1>"Bedrer,Svekker"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C39" type="list">
-      <formula1>"Bedrer,Svekker"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C40" type="list">
-      <formula1>"Bedrer,Svekker"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C47" type="list">
@@ -2603,226 +2696,226 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>90</v>
+      <c r="B2" s="26" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>94</v>
+      <c r="B5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="28" t="n">
+      <c r="B6" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="29" t="n">
         <v>9791325</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>96</v>
+      <c r="D6" s="28" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="27" t="s">
-        <v>98</v>
+      <c r="B7" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="28" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="27" t="s">
-        <v>100</v>
+      <c r="B8" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="28" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="27" t="s">
-        <v>102</v>
+      <c r="B9" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="28" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="27" t="s">
-        <v>104</v>
+      <c r="B10" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="28" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="27" t="s">
-        <v>106</v>
+      <c r="B11" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="28" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="27" t="s">
-        <v>108</v>
+      <c r="B12" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="27" t="s">
-        <v>110</v>
+      <c r="B13" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="28" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="27" t="s">
-        <v>112</v>
+      <c r="B14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="28" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="27" t="s">
-        <v>114</v>
+      <c r="B15" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="28" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="27" t="s">
-        <v>116</v>
+      <c r="B16" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="28" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="27" t="s">
-        <v>118</v>
+      <c r="B17" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="28" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="27" t="s">
-        <v>120</v>
+      <c r="B18" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="27" t="s">
-        <v>122</v>
+      <c r="B19" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="28" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="27" t="s">
-        <v>124</v>
+      <c r="B20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="28" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="27" t="s">
-        <v>126</v>
+      <c r="B21" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="28" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="27" t="s">
-        <v>128</v>
+      <c r="B22" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="28" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="27" t="s">
-        <v>130</v>
+      <c r="B23" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="29"/>
+      <c r="D23" s="28" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="27" t="s">
-        <v>132</v>
+      <c r="B24" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="28" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="27" t="s">
-        <v>134</v>
+      <c r="B25" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="29"/>
+      <c r="D25" s="28" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="27" t="s">
-        <v>136</v>
+      <c r="B26" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="29"/>
+      <c r="D26" s="28" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="27" t="s">
-        <v>138</v>
+      <c r="B27" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="29"/>
+      <c r="D27" s="28" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok04/OK04_Regnskapsanalyse_Oppgaver_v6.xlsx
+++ b/pensum/ok04/OK04_Regnskapsanalyse_Oppgaver_v6.xlsx
@@ -187,7 +187,7 @@
     <t xml:space="preserve">Overskuddet er feil regnet, fordi skatten ikke er trukket fra</t>
   </si>
   <si>
-    <t xml:space="preserve">Det er januar 2027, og årsregnskapet for 2026 er klart med et årsresultat på 910 650 kr. Tom Berg vil ta ut 600 000 kr i utbytte: «Pengene finnes, vi hadde jo overskudd.» Utbyttet skal betales fra bankkontoen. Kari Nordlund vil vite hva det gjør med betalingsevnen og soliditeten før hun svarer, for banken skal fornye kassekreditten i mars.</t>
+    <t xml:space="preserve">Det er mai 2027. Årsregnskapet for 2026 er fastsatt med et årsresultat på 910 650 kr, og styret skal foreslå utbytte for generalforsamlingen. Tom Berg vil ha 600 000 kr i utbytte: «Pengene finnes, vi hadde jo overskudd.» Utbyttet skal betales fra bankkontoen. Kari Nordlund vil vite hva det gjør med betalingsevnen og soliditeten før hun svarer, for banken skal fornye kassekreditten i juni. Dere regner på balansen per 31.12.2026, slik banken og styret leser den.</t>
   </si>
   <si>
     <t xml:space="preserve">Likviditetsgrad 1 = omløpsmidler × 100 / kortsiktig gjeld (bokas normtall 200 %; bransjen ligger på 190 %). Likviditetsgrad 2 = (omløpsmidler − varelager) × 100 / kortsiktig gjeld (normtall 100 %; bransjen 160 %). Egenkapitalandel = egenkapital × 100 / totalkapital. Et utbytte som betales ut, tar pengene fra bankinnskuddet og fra egenkapitalen samtidig, og totalkapitalen blir like mye mindre.</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">Svekker</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS i Oslo har drevet i ett år. Eieren vil kjøpe en tredje servicebil for 400 000 kr på nytt banklån, og banken ber om årsregnskapet først. Du er den som skal legge fram tallene: lønnsomhet, likviditet og soliditet, og si hva som er sterkt og hva som er svakt. Sammenlikn med bransjen: elektrobedriftene i NHO Elektros lønnsomhetsrapport 2025 hadde totalkapitalrentabilitet 14,6 %, driftsresultat 7,5 % av omsetningen, likviditetsgrad 1 på 190 %, likviditetsgrad 2 på 160 % og egenkapitalandel 36,4 %.</t>
+    <t xml:space="preserve">Fjell Elektro AS i Oslo har drevet i ett år. Fjell leaser to servicebiler. Eieren vil kjøpe en brukt servicebil til seg selv for 400 000 kr på nytt banklån, i stedet for å lease den tredje, og banken ber om årsregnskapet først. Du er den som skal legge fram tallene: lønnsomhet, likviditet og soliditet, og si hva som er sterkt og hva som er svakt. Sammenlikn med bransjen: elektrobedriftene i NHO Elektros lønnsomhetsrapport 2025 hadde totalkapitalrentabilitet 14,6 %, driftsresultat 7,5 % av omsetningen, likviditetsgrad 1 på 190 %, likviditetsgrad 2 på 160 % og egenkapitalandel 36,4 %.</t>
   </si>
   <si>
     <t xml:space="preserve">Driftsmargin = driftsresultat × 100 / salgsinntekt. Totalkapitalrentabilitet = (resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital. Likviditetsgrad 1 = omløpsmidler × 100 / kortsiktig gjeld. Likviditetsgrad 2 = (omløpsmidler − varelager) × 100 / kortsiktig gjeld. Egenkapitalandel = egenkapital × 100 / totalkapital. Gjeldsgrad = sum gjeld / egenkapital (bør ikke være over 5). Egenkapitalandelen bedres bare ved å la overskudd stå, betale ned gjeld eller skyte inn ny egenkapital.</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">1. Lønnsomhet: regn driftsmarginen og totalkapitalrentabiliteten. Gjennomsnittlig totalkapital er (800 000 + 1 383 257) / 2. Svar med én desimal.
 2. Likviditet: regn likviditetsgrad 1 og 2 per 31. desember.
 3. Soliditet: regn egenkapitalandelen og gjeldsgraden per 31. desember. Gjeldsgraden svarer du med to desimaler, og den er et forholdstall, ikke en prosent.
-4. Eieren vil kjøpe en tredje servicebil for 400 000 kr på nytt banklån. Velg for hvert av de seks tiltakene i g om det bedrer eller svekker egenkapitalandelen.
+4. Eieren vil kjøpe en brukt servicebil til seg selv for 400 000 kr på nytt banklån, i stedet for å lease den tredje. Velg for hvert av de seks tiltakene i g om det bedrer eller svekker egenkapitalandelen.
 5. Skriv bankens vurdering i h: er Fjell lønnsom nok, klarer den regningene, og tåler den et dårlig år?</t>
   </si>
   <si>
@@ -1643,7 +1643,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>52</v>
       </c>

--- a/pensum/ok04/OK04_Regnskapsanalyse_Oppgaver_v6.xlsx
+++ b/pensum/ok04/OK04_Regnskapsanalyse_Oppgaver_v6.xlsx
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1096,27 +1096,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="14" t="s">
         <v>44</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="90" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
         <v>65</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="9" t="s">
         <v>72</v>
       </c>
